--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE12"/>
+  <dimension ref="A1:BE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,160 +714,160 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -881,160 +881,160 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -1048,160 +1048,160 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="G4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="S4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="T4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="U4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="V4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="W4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="5">
@@ -1215,160 +1215,160 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AK5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BC5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1382,1216 +1382,1383 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Auth &amp; Identity Management</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>80</v>
-      </c>
-      <c r="E7" t="n">
-        <v>78</v>
-      </c>
+          <t>Management Net Capacity</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Real-time Analytics</t>
+          <t>Auth &amp; Identity Management</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>119.6</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mobile App Redesign</t>
+          <t>Real-time Analytics</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>98.8</v>
+        <v>119.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>API Gateway Optimization</t>
+          <t>Mobile App Redesign</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>41.6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="X10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Data Quality Framework</t>
+          <t>API Gateway Optimization</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>88.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data Quality Framework</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Weekly Allocation</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.4</v>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE13"/>
+  <dimension ref="A1:BE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,160 +881,160 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -1048,160 +1048,160 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="W4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="5">
@@ -1382,160 +1382,160 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1549,160 +1549,160 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="X7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -2077,163 +2077,163 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>41.6</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -2591,175 +2591,814 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Weekly Allocation</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Engineers capacity</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Managers capacity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Engineers absence</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Managers absence</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Weekly Allocation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -444,67 +444,67 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>Mar.30</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>Apr.06</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>Apr.13</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>Apr.20</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>Apr.27</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>May.04</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>May.11</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>May.18</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>May.25</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>Jun.01</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>Jun.08</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>Jun.15</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>Jun.22</t>
         </is>
       </c>
     </row>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,320 +1109,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Weekly Allocation</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Engineers capacity</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Managers capacity</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Engineers absence</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Managers absence</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Weekly Allocation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R18" t="n">
         <v>4.3</v>
       </c>
     </row>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -569,43 +569,43 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -619,43 +619,43 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5">
@@ -826,46 +826,46 @@
         <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>55.9</v>
+        <v>62.4</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -1123,43 +1123,43 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -811,181 +811,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Auth &amp; Identity Management</t>
+          <t>Alpha Search</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>62.4</v>
+        <v>7.8</v>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="R8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real-time Analytics</t>
+          <t>Beta Platform</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mobile App Redesign</t>
+          <t>Gamma Onboarding</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -996,116 +996,116 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>API Gateway Optimization</t>
+          <t>Delta Infra</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Quality Framework</t>
+          <t>Epsilon Compliance</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -1123,43 +1123,43 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,65 +444,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Off Estimate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Mar.30</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Apr.06</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Apr.13</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Apr.20</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Apr.27</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>May.04</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>May.11</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>May.18</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>May.25</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Jun.01</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Jun.08</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Jun.15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Jun.22</t>
         </is>
@@ -518,9 +523,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>5</v>
       </c>
@@ -555,6 +558,9 @@
         <v>5</v>
       </c>
       <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -568,9 +574,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0.2</v>
       </c>
@@ -605,6 +609,9 @@
         <v>0.2</v>
       </c>
       <c r="R3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -618,9 +625,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>4.8</v>
       </c>
@@ -655,6 +660,9 @@
         <v>4.8</v>
       </c>
       <c r="R4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S4" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -668,9 +676,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>2</v>
       </c>
@@ -705,6 +711,9 @@
         <v>2</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -718,9 +727,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0.3</v>
       </c>
@@ -755,6 +762,9 @@
         <v>0.3</v>
       </c>
       <c r="R6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -768,9 +778,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1.7</v>
       </c>
@@ -807,6 +815,9 @@
       <c r="R7" t="n">
         <v>1.7</v>
       </c>
+      <c r="S7" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -826,46 +837,49 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6</v>
+        <v>8</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -886,46 +900,49 @@
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9</v>
+        <v>12</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -948,8 +965,8 @@
       <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.4</v>
+      <c r="F10" t="b">
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -985,6 +1002,9 @@
         <v>0.4</v>
       </c>
       <c r="R10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1006,46 +1026,49 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1066,46 +1089,49 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2</v>
+        <v>3</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1120,46 +1146,102 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Off Capacity</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Epic / Capacity Metric</t>
+          <t>Epic Description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Management Capacity</t>
+          <t>Management Capacity (Bruto)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>

--- a/data/examples/output_example.xlsx
+++ b/data/examples/output_example.xlsx
@@ -52,6 +52,83 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00548235"/>
+          <bgColor rgb="00548235"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00B4C6E7"/>
+          <bgColor rgb="00B4C6E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D2E9"/>
+          <bgColor rgb="00D9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+          <bgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+          <bgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+          <bgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -522,7 +599,9 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>5</v>
@@ -573,7 +652,9 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0.2</v>
@@ -624,7 +705,9 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>62.4</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>4.8</v>
@@ -675,7 +758,9 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>26</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>2</v>
@@ -726,7 +811,9 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>3.9</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0.3</v>
@@ -777,7 +864,9 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>22.1</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1.7</v>
@@ -1245,6 +1334,42 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F8:F12">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>F8=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14:S14">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>G14=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:S14">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="0">
+      <formula>$A2="Self-Service ML EV Range - Phase 1"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
+      <formula>$A2="Quality improvements through ML/AI experimentation"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="0">
+      <formula>$A2="Maintenance &amp; Release"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4" stopIfTrue="0">
+      <formula>$A2="Security &amp; Compliance"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="5" stopIfTrue="0">
+      <formula>$A2="Customer Support"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="6" stopIfTrue="0">
+      <formula>$A2="Critical Technical Debt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="7" stopIfTrue="0">
+      <formula>$A2="Critical Product Debt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="8" stopIfTrue="0">
+      <formula>$A2="Critical Customer Commitments"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>